--- a/src/bases/treated/dados_pedras_processado_2026-03-07.xlsx
+++ b/src/bases/treated/dados_pedras_processado_2026-03-07.xlsx
@@ -425,1392 +425,1541 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>PEDRA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>IPV</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>IPS</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IAN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>IEG</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>INDE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IAA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>IDA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>72</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>15</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>17.55</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>38.1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>89</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>56.66</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>39</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>75</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>22.99</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>41</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>45.13</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>72</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>67</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>64.66</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>51</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>93.31</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>56</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>74.92</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>84.69</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>12.48</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>38</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>40</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>89.83</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>40.79</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>79</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>5.28</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Onix</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>41</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>58</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>44.75</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>46.85</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>31.57</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Onix</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>73.17</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>42.65</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>78</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Quartzo</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>13</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>78</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>40.73</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>32.29</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>77</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>31.38</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>60</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>53</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>25.96</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>21.48</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>59</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>76.33</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>49</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>48</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>87.2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>34.82</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>32</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>16.78</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Topazio</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>18</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>72</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>63.9</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>43.64</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>57.78</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Rubi</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>32</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>35.71</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>6.09</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>30</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>50.18</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Quartzo</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>36</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>54.66</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>42.74</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>77</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>77.11</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Rubi</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>22</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>99</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>38.84</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>39.39</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>86</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>87.3</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>93</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>33</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>61.96</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>14.68</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>86</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>9.15</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>63</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>60</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>66.52</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>56.7</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>25</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>53.89</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Topazio</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>53</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>27</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>37.35</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>42</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>42.53</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>95</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>87</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>56.58</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>7.62</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>93</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>84.48999999999999</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>98</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>40</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>36</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>52.9</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>77.55</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>85</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>70.89</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>93</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Rubi</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>38</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>32</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>81.66</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>72.05</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>45</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>39.79</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="C22" t="n">
         <v>74</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>43</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>42.55</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>18.06</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>87</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>0.52</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="C23" t="n">
         <v>31</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>61</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>76.06999999999999</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>49.68</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>52</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>96.34</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Rubi</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>54</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>80.88</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>57.69</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>92</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>21.66</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Rubi</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="C25" t="n">
         <v>25</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>52</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>63.6</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>76</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>42.34</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>40</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>45.67</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>87.67</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>69</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>3.71</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>69</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>65</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>99.87</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>90.62</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>75</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>7.87</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Turmalina</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="C28" t="n">
         <v>74</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>71</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>53.06</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>67</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>42.93</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>39.22</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>43.04</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>34</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4.86</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="C30" t="n">
         <v>40</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>94</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>37.77</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>65</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>7.26</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="C31" t="n">
         <v>62</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>95</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>24.47</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>61.45</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>82</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>47.47</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Onix</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="C32" t="n">
         <v>58</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>22</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>73.62</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>64</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>91.47</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Topazio</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="C33" t="n">
         <v>62</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>63</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>44.26</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>71.38</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>23</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>19.03</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>Quartzo</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="C34" t="n">
         <v>34</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>44</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>96.29000000000001</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>59.91</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>44</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>17.54</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Quartzo</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="C35" t="n">
         <v>82</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>14</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>6.63</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>10</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>23.72</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Onix</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="C36" t="n">
         <v>86</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>13</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>17.38</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>95.31999999999999</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>85</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>93.19</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Esmeralda</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="C37" t="n">
         <v>44</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>96.29000000000001</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>98.45</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>56</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>39.08</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Topazio</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="C38" t="n">
         <v>86</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>35</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>43.72</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>67</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>26.11</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="C39" t="n">
         <v>1</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>71</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>50.06</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>99.28</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>43</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>56.06</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Topazio</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="C40" t="n">
         <v>29</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>73.38</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>42.63</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>74</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>46.05</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>93</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="C41" t="n">
         <v>89</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>64</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>42.76</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>80.3</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>95</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>24.88</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Onix</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="C42" t="n">
         <v>6</v>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>36</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>79.53</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>73.08</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>64</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>92.27</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="C43" t="n">
         <v>37</v>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>53</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>16.76</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>61.5</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>64</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>6.9</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Safira</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="C44" t="n">
         <v>79</v>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>89</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>82.81</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>11.93</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>6</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>31.26</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Onix</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="C45" t="n">
         <v>83</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>17</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>35.04</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>44.36</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>60</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>88.62</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Ametista</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="C46" t="n">
         <v>66</v>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>86</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>24.93</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>34.18</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>44</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>40.93</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Turmalina</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="C47" t="n">
         <v>29</v>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>6</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>48.94</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>9</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>92.65000000000001</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Quartzo</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="C48" t="n">
         <v>15</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>20</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>30</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>40</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>50</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>60</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Rubi</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="C49" t="n">
         <v>10</v>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>20</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>40</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>50</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>60</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>70</v>
       </c>
     </row>
